--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="226">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -113,7 +113,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ImmunizationEvaluation</t>
+    <t>http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-immunizationevaluation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: Argonaut-DQ-DSTU2</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -266,6 +269,9 @@
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
 dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+  </si>
+  <si>
+    <t>CarePlan</t>
   </si>
   <si>
     <t>Event</t>
@@ -500,12 +506,15 @@
 </t>
   </si>
   <si>
-    <t>Business identifier</t>
+    <t>(QI) Business identifier</t>
   </si>
   <si>
     <t>A unique identifier assigned to this immunization evaluation record.</t>
   </si>
   <si>
+    <t>CarePlan.subject</t>
+  </si>
+  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -515,7 +524,7 @@
     <t>ImmunizationEvaluation.status</t>
   </si>
   <si>
-    <t>completed | entered-in-error</t>
+    <t>(QI) completed | entered-in-error</t>
   </si>
   <si>
     <t>Indicates the current status of the evaluation of the vaccination administration event.</t>
@@ -539,11 +548,11 @@
     <t>ImmunizationEvaluation.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
-    <t>Who this evaluation is for</t>
+    <t>(QI) Who this evaluation is for</t>
   </si>
   <si>
     <t>The individual for whom the evaluation is being done.</t>
@@ -565,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t>Date evaluation was performed</t>
+    <t>(QI) Date evaluation was performed</t>
   </si>
   <si>
     <t>The date the evaluation of the vaccine administration event was performed.</t>
@@ -583,7 +592,7 @@
     <t>ImmunizationEvaluation.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -603,16 +612,13 @@
 </t>
   </si>
   <si>
-    <t>Evaluation target disease</t>
+    <t>(QI) Evaluation target disease</t>
   </si>
   <si>
     <t>The vaccine preventable disease the dose is being evaluated against.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-evaluation-target-disease|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-evaluation-target-disease</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = ( 30956-7 | 38890-0 )</t>
@@ -621,11 +627,11 @@
     <t>ImmunizationEvaluation.immunizationEvent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Immunization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/immunization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
-    <t>Immunization being evaluated</t>
+    <t>(QI) Immunization being evaluated</t>
   </si>
   <si>
     <t>The vaccine administration event being evaluated.</t>
@@ -634,16 +640,13 @@
     <t>ImmunizationEvaluation.doseStatus</t>
   </si>
   <si>
-    <t>Status of the dose relative to published recommendations</t>
+    <t>(QI) Status of the dose relative to published recommendations</t>
   </si>
   <si>
     <t>Indicates if the dose is valid or not valid with respect to the published recommendations.</t>
   </si>
   <si>
-    <t>The status of the administered dose relative to the published recommendations for the target disease.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-evaluation-dose-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-evaluation-dose-status</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = ( 59781-5 )</t>
@@ -652,16 +655,10 @@
     <t>ImmunizationEvaluation.doseStatusReason</t>
   </si>
   <si>
-    <t>Reason for the dose status</t>
+    <t>(QI) Reason for the dose status</t>
   </si>
   <si>
     <t>Provides an explanation as to why the vaccine administration event is valid or not relative to the published recommendations.</t>
-  </si>
-  <si>
-    <t>The reason the dose status was assigned.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-evaluation-dose-status-reason|4.0.1</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = ( 30982-3 )</t>
@@ -1025,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AO24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.5234375" customWidth="true" bestFit="true"/>
@@ -1038,7 +1035,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.69921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1052,8 +1049,8 @@
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="83.0234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="33.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.28125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
@@ -1063,10 +1060,11 @@
     <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="31.33984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="29.45703125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="20.3359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.33984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="20.3359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,6 +1188,9 @@
       <c r="AN1" t="s" s="1">
         <v>76</v>
       </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1204,10 +1205,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1219,13 +1220,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1279,36 +1280,39 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
+      </c>
+      <c r="AO2" t="s" s="2">
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1316,10 +1320,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1328,19 +1332,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1390,13 +1394,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1414,15 +1418,18 @@
         <v>20</v>
       </c>
       <c r="AN3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1430,10 +1437,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1442,16 +1449,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1502,19 +1509,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1526,15 +1533,18 @@
         <v>20</v>
       </c>
       <c r="AN4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1542,31 +1552,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1616,19 +1626,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1640,15 +1650,18 @@
         <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1656,10 +1669,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1671,16 +1684,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1706,13 +1719,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1730,19 +1743,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1754,26 +1767,29 @@
         <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1785,16 +1801,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1844,19 +1860,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1868,26 +1884,29 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>122</v>
+        <v>20</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1899,16 +1918,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1958,13 +1977,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1982,15 +2001,18 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1998,10 +2020,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2013,13 +2035,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2058,29 +2080,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2092,28 +2114,31 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2125,13 +2150,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2182,19 +2207,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2206,50 +2231,53 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2298,19 +2326,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2322,15 +2350,18 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>130</v>
+        <v>20</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2338,10 +2369,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2353,13 +2384,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2410,39 +2441,42 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2450,28 +2484,28 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2498,63 +2532,66 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>158</v>
-      </c>
       <c r="AG13" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2562,10 +2599,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2574,16 +2611,16 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2634,39 +2671,42 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2674,10 +2714,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2689,13 +2729,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2746,39 +2786,42 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2786,10 +2829,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2801,13 +2844,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2858,39 +2901,42 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2898,10 +2944,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2910,16 +2956,16 @@
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2946,63 +2992,64 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y17" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y17" s="2"/>
+      <c r="Z17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3010,10 +3057,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3022,16 +3069,16 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3082,19 +3129,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3106,15 +3153,18 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3122,10 +3172,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3134,16 +3184,16 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3170,13 +3220,11 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3194,39 +3242,42 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3234,10 +3285,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3249,13 +3300,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3282,63 +3333,64 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AA20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3346,10 +3398,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3361,13 +3413,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3418,39 +3470,42 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AN21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3458,10 +3513,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3473,13 +3528,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3530,19 +3585,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3554,15 +3609,18 @@
         <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3570,10 +3628,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3585,16 +3643,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3644,39 +3702,42 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3684,10 +3745,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3699,16 +3760,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>225</v>
-      </c>
       <c r="N24" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3758,30 +3819,33 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="AN24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>20</v>
       </c>
     </row>

--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-immunizationevaluation-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e-constrained ImmunizationEvaluation profile derived from FHIR R4 ImmunizationEvaluation.
+    <t>314e-constrained ImmunizationEvaluation profile derived from QI-Core ImmunizationEvaluation.
 This profile applies 314e-defined extensions and uses 314e datatype profiles
 where applicable.</t>
   </si>
